--- a/Sprint Planning/Product Backlog - SOEN 341.xlsx
+++ b/Sprint Planning/Product Backlog - SOEN 341.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gagne\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF9703DF-2742-4BB7-AF0A-36E945CCA3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{455DBB0B-D2BC-4996-B66D-4A1450130EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{9FF516DD-DD1A-4540-862E-5B2452513E79}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" firstSheet="1" activeTab="2" xr2:uid="{9FF516DD-DD1A-4540-862E-5B2452513E79}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover Page" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="69">
   <si>
     <t>The Cool Team</t>
   </si>
@@ -265,6 +265,11 @@
 Link the allergies/preferences to the user</t>
   </si>
   <si>
+    <t>Setup the recipe display page
+Improved UI for the display page
+Helped with "Add recipe"</t>
+  </si>
+  <si>
     <t>Created the GitHub, and helped fill out the product backlog.
 Setup the login and registration page.
 Setup the main menu and the profile page.
@@ -277,6 +282,28 @@
   <si>
     <t>found and setup the database and website host
 setup and debugged connectivity between website and database</t>
+  </si>
+  <si>
+    <t>Created acceptance tests for sprint 1 user stories
+Setup continuous integration pipeline</t>
+  </si>
+  <si>
+    <t>Added the recipe tables in the database
+Setup the add recipe function
+Helped with the recipe display
+Helped with the edit recipes
+Helped with the delete recipes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setup the edit recipe function, and the remove recipe function. </t>
+  </si>
+  <si>
+    <t>Redesigned Recipes page layout
+Standardized styling across Add Recipe, Edit Recipe, and Recipes pages.
+Fixed Edit/Delete button alignment and styling</t>
+  </si>
+  <si>
+    <t>Setup the recipe filtering, sorting and searching</t>
   </si>
 </sst>
 </file>
@@ -1251,7 +1278,6 @@
     <mergeCell ref="F11:I11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1560,7 +1586,7 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A12" s="46">
         <v>11</v>
       </c>
@@ -1691,7 +1717,7 @@
     <col min="1" max="1" width="38.1796875" customWidth="1"/>
     <col min="2" max="2" width="31.54296875" customWidth="1"/>
     <col min="3" max="3" width="53.54296875" customWidth="1"/>
-    <col min="4" max="4" width="48.7265625" customWidth="1"/>
+    <col min="4" max="4" width="57.26953125" customWidth="1"/>
     <col min="5" max="5" width="47.7265625" customWidth="1"/>
     <col min="6" max="6" width="62.81640625" customWidth="1"/>
   </cols>
@@ -1724,12 +1750,14 @@
       <c r="C3" s="14">
         <v>6</v>
       </c>
-      <c r="D3" s="14"/>
+      <c r="D3" s="14">
+        <v>4</v>
+      </c>
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
       <c r="G3" s="11">
         <f>SUM(C3:F3)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1740,7 +1768,9 @@
       <c r="C4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="15"/>
+      <c r="D4" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
       <c r="G4" s="12"/>
@@ -1753,17 +1783,19 @@
         <v>56</v>
       </c>
       <c r="C5" s="14">
-        <v>8</v>
-      </c>
-      <c r="D5" s="14"/>
+        <v>6</v>
+      </c>
+      <c r="D5" s="14">
+        <v>4</v>
+      </c>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
       <c r="G5" s="11">
         <f>SUM(C5:F5)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="66.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="64"/>
       <c r="B6" s="7" t="s">
         <v>57</v>
@@ -1771,7 +1803,9 @@
       <c r="C6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="15"/>
+      <c r="D6" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="E6" s="15"/>
       <c r="F6" s="15"/>
       <c r="G6" s="12"/>
@@ -1786,23 +1820,27 @@
       <c r="C7" s="14">
         <v>10</v>
       </c>
-      <c r="D7" s="14"/>
+      <c r="D7" s="14">
+        <v>10</v>
+      </c>
       <c r="E7" s="14"/>
       <c r="F7" s="14"/>
       <c r="G7" s="11">
         <f>SUM(C7:F7)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="66.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="66"/>
       <c r="B8" s="7" t="s">
         <v>57</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="15"/>
+        <v>61</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
       <c r="G8" s="12"/>
@@ -1817,12 +1855,14 @@
       <c r="C9" s="14">
         <v>2</v>
       </c>
-      <c r="D9" s="14"/>
+      <c r="D9" s="14">
+        <v>4</v>
+      </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
       <c r="G9" s="11">
         <f>SUM(C9:F9)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -1831,9 +1871,11 @@
         <v>57</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="15"/>
+        <v>62</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>68</v>
+      </c>
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
       <c r="G10" s="12"/>
@@ -1848,12 +1890,14 @@
       <c r="C11" s="16">
         <v>5</v>
       </c>
-      <c r="D11" s="16"/>
+      <c r="D11" s="16">
+        <v>4</v>
+      </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="G11" s="11">
         <f>SUM(C11:F11)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1862,9 +1906,11 @@
         <v>57</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="15"/>
+        <v>63</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
       <c r="G12" s="13"/>
@@ -1877,12 +1923,14 @@
         <v>56</v>
       </c>
       <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
+      <c r="D13" s="16">
+        <v>4</v>
+      </c>
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="11">
         <f>SUM(C13:F13)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1891,7 +1939,9 @@
         <v>57</v>
       </c>
       <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
+      <c r="D14" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="E14" s="15"/>
       <c r="F14" s="15"/>
       <c r="G14" s="13"/>

--- a/Sprint Planning/Product Backlog - SOEN 341.xlsx
+++ b/Sprint Planning/Product Backlog - SOEN 341.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gagne\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{455DBB0B-D2BC-4996-B66D-4A1450130EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23A24889-1192-4112-8A16-D5EBA4173EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" firstSheet="1" activeTab="2" xr2:uid="{9FF516DD-DD1A-4540-862E-5B2452513E79}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" firstSheet="2" activeTab="2" xr2:uid="{9FF516DD-DD1A-4540-862E-5B2452513E79}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover Page" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
   <si>
     <t>The Cool Team</t>
   </si>
@@ -259,6 +259,14 @@
 Added a consistent top header (logo + app name) across pages for a cleaner layout</t>
   </si>
   <si>
+    <t>Redesigned Recipes page layout
+Standardized styling across Add Recipe, Edit Recipe, and Recipes pages.
+Fixed Edit/Delete button alignment and styling</t>
+  </si>
+  <si>
+    <t>Designed the UI for the recipe creator page</t>
+  </si>
+  <si>
     <t>Helped Setup the Github page by creating the GitHub issues
 Display the user's  dietary preferences on the profile page
 Store the allergies and dietary preferences data
@@ -270,22 +278,16 @@
 Helped with "Add recipe"</t>
   </si>
   <si>
+    <t>Added the weekly schedule to display the recipes chosen
+Added styling for the weekly schedule
+Added an error box if duplicate is added
+Helped with the recipe creation function</t>
+  </si>
+  <si>
     <t>Created the GitHub, and helped fill out the product backlog.
 Setup the login and registration page.
 Setup the main menu and the profile page.
 Added the allergies in the profile page.</t>
-  </si>
-  <si>
-    <t>Helped set up Github files, and fill product backlog. 
-Kept record of meeting minutes</t>
-  </si>
-  <si>
-    <t>found and setup the database and website host
-setup and debugged connectivity between website and database</t>
-  </si>
-  <si>
-    <t>Created acceptance tests for sprint 1 user stories
-Setup continuous integration pipeline</t>
   </si>
   <si>
     <t>Added the recipe tables in the database
@@ -295,15 +297,42 @@
 Helped with the delete recipes</t>
   </si>
   <si>
+    <t>Added the recipe creation function
+Added the styling to the calorie tracker page and debugged it
+Helped with the main menu schedule
+Helped with the calorie tracker
+Refactored code to have functions instead of duplicate code</t>
+  </si>
+  <si>
+    <t>Helped set up Github files, and fill product backlog. 
+Kept record of meeting minutes</t>
+  </si>
+  <si>
+    <t>Setup the recipe filtering, sorting and searching</t>
+  </si>
+  <si>
+    <t>Helped with claorie tracker and profile</t>
+  </si>
+  <si>
+    <t>found and setup the database and website host
+setup and debugged connectivity between website and database</t>
+  </si>
+  <si>
+    <t>Created acceptance tests for sprint 1 user stories
+Setup continuous integration pipeline</t>
+  </si>
+  <si>
+    <t>Updated Continuous Integration pipeline to utilize unit tests
+Created unit tests for sprint 1 and 2 features</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joined the team a bit late and was overseas. </t>
+  </si>
+  <si>
     <t xml:space="preserve">Setup the edit recipe function, and the remove recipe function. </t>
   </si>
   <si>
-    <t>Redesigned Recipes page layout
-Standardized styling across Add Recipe, Edit Recipe, and Recipes pages.
-Fixed Edit/Delete button alignment and styling</t>
-  </si>
-  <si>
-    <t>Setup the recipe filtering, sorting and searching</t>
+    <t>Wrote some Acceptance Tests for some User Stories by testing the platform. With help, did the calorie tracker</t>
   </si>
 </sst>
 </file>
@@ -786,6 +815,42 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -802,42 +867,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1191,18 +1220,18 @@
   </cols>
   <sheetData>
     <row r="5" spans="6:9" x14ac:dyDescent="0.35">
-      <c r="F5" s="54" t="s">
+      <c r="F5" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
     </row>
     <row r="6" spans="6:9" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
     </row>
     <row r="7" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="F7" s="52"/>
@@ -1211,60 +1240,60 @@
       <c r="I7" s="52"/>
     </row>
     <row r="8" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="F8" s="55" t="s">
+      <c r="F8" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
     </row>
     <row r="9" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="F9" s="53" t="s">
+      <c r="F9" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
     </row>
     <row r="10" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="65"/>
     </row>
     <row r="11" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="F11" s="53" t="s">
+      <c r="F11" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
     </row>
     <row r="12" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="F12" s="53" t="s">
+      <c r="F12" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
     </row>
     <row r="13" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="F13" s="53" t="s">
+      <c r="F13" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
     </row>
     <row r="14" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="F14" s="53" t="s">
+      <c r="F14" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1509,54 +1538,54 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="80.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="41">
+      <c r="A9" s="17">
         <v>8</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="44">
+      <c r="D9" s="20">
         <v>6</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="44" t="s">
+      <c r="F9" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="43" t="s">
+      <c r="G9" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="45">
+      <c r="H9" s="21">
         <v>46126</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="41">
+      <c r="A10" s="17">
         <v>9</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="44">
+      <c r="D10" s="20">
         <v>7</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="G10" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="H10" s="45">
+      <c r="H10" s="21">
         <v>46126</v>
       </c>
     </row>
@@ -1613,11 +1642,11 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="58"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="70"/>
       <c r="D13" s="5">
         <f>SUM(D2:D12)</f>
         <v>46</v>
@@ -1741,7 +1770,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="55" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -1753,15 +1782,17 @@
       <c r="D3" s="14">
         <v>4</v>
       </c>
-      <c r="E3" s="14"/>
+      <c r="E3" s="14">
+        <v>5</v>
+      </c>
       <c r="F3" s="14"/>
       <c r="G3" s="11">
         <f>SUM(C3:F3)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="62"/>
+      <c r="A4" s="56"/>
       <c r="B4" s="7" t="s">
         <v>57</v>
       </c>
@@ -1769,14 +1800,16 @@
         <v>58</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="15"/>
+        <v>59</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>60</v>
+      </c>
       <c r="F4" s="15"/>
       <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="57" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -1788,30 +1821,34 @@
       <c r="D5" s="14">
         <v>4</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="14">
+        <v>15</v>
+      </c>
       <c r="F5" s="14"/>
       <c r="G5" s="11">
         <f>SUM(C5:F5)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="64"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="101.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="58"/>
       <c r="B6" s="7" t="s">
         <v>57</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="15"/>
+        <v>62</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="F6" s="15"/>
       <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="65" t="s">
+      <c r="A7" s="59" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -1823,30 +1860,34 @@
       <c r="D7" s="14">
         <v>10</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="14">
+        <v>20</v>
+      </c>
       <c r="F7" s="14"/>
       <c r="G7" s="11">
         <f>SUM(C7:F7)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="76.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="66"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="60"/>
       <c r="B8" s="7" t="s">
         <v>57</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="15"/>
+      <c r="E8" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="F8" s="15"/>
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="67" t="s">
+      <c r="A9" s="61" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -1858,30 +1899,34 @@
       <c r="D9" s="14">
         <v>4</v>
       </c>
-      <c r="E9" s="14"/>
+      <c r="E9" s="14">
+        <v>5</v>
+      </c>
       <c r="F9" s="14"/>
       <c r="G9" s="11">
         <f>SUM(C9:F9)</f>
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="68"/>
+      <c r="A10" s="62"/>
       <c r="B10" s="7" t="s">
         <v>57</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="15"/>
+      <c r="E10" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="F10" s="15"/>
       <c r="G10" s="12"/>
     </row>
     <row r="11" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="69" t="s">
+      <c r="A11" s="63" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -1893,56 +1938,68 @@
       <c r="D11" s="16">
         <v>4</v>
       </c>
-      <c r="E11" s="16"/>
+      <c r="E11" s="16">
+        <v>12</v>
+      </c>
       <c r="F11" s="16"/>
       <c r="G11" s="11">
         <f>SUM(C11:F11)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="70"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="52.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="64"/>
       <c r="B12" s="7" t="s">
         <v>57</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="15"/>
+        <v>71</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="F12" s="15"/>
       <c r="G12" s="13"/>
     </row>
     <row r="13" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="53" t="s">
         <v>4</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="16"/>
+      <c r="C13" s="16">
+        <v>0</v>
+      </c>
       <c r="D13" s="16">
         <v>4</v>
       </c>
-      <c r="E13" s="16"/>
+      <c r="E13" s="16">
+        <v>5</v>
+      </c>
       <c r="F13" s="16"/>
       <c r="G13" s="11">
         <f>SUM(C13:F13)</f>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="60"/>
+      <c r="A14" s="54"/>
       <c r="B14" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="15"/>
+      <c r="C14" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="D14" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="15"/>
+        <v>74</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="F14" s="15"/>
       <c r="G14" s="13"/>
     </row>
